--- a/关键思路.xlsx
+++ b/关键思路.xlsx
@@ -1,179 +1,246 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_940CFBEED80547B5BF88692ABC71E2AF"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="617220" y="182880"/>
+          <a:ext cx="8395970" cy="5789295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>为我再详细解释一下你做这张图的逻辑，包括如下部分：
+1. 精准定义你对于每个色区（zone）的定义
+2. 根据你的定义，找一定的reference来支撑你的结论
+3. 对于我们图中的量纲给出严格的定义</t>
+  </si>
+  <si>
+    <t>The ROYGBIV acronym denotes the conventional sequence of hues in the visible spectrum—Red, Orange, Yellow, Green, Blue, Indigo, and Violet—first systematically partitioned by Isaac Newton in his seminal treatise Opticks . Newton divided the spectrum into seven colors to correspond with the seven notes of the diatonic musical scale, establishing a foundational perceptual framework for color representation. 
+Following the classic ROYGBIV spectral partitioning as a perceptually motivated proxy for color similarity, consistent with modern practices in representation learning (Caron et al., ICCV 2021),this classic partitioning has since served as a standard reference for discrete color zoning in visualization and representation learning tasks, providing a perceptually motivated proxy for semantic similarity in high-dimensional embedding spaces.</t>
+  </si>
+  <si>
+    <t>To assess whether th
+e proposed Pixel Embedding learns perceptually meaningful representations, we perform a controlled visualization experiment using 140 synthetic pixels partitioned into seven color zones. We first convert the RGB pixel values to the HSV color space, which separates hue (representing color type) from saturation and value. The hue channel is then quantized into seven discrete intervals to obtain perceptually motivated zone labels, following the color modeling and representation analysis approaches in Muratbekova et al. (2026) and Caron et al. (2021). Embeddings from both the baseline LLM tokenizer and our Pixel Embedding (augmented with intra-patch positional encoding and optional channel encoding) are projected into two dimensions via t-SNE or UMAP and further examined through cosine similarity matrices. This procedure enables direct visual and quantitative comparison of clustering structure between the two representation methods.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,157 +540,163 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -678,74 +751,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1007,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="55.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="72.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="81.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="C1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="250" customHeight="1" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <f>_xlfn.DISPIMG("ID_940CFBEED80547B5BF88692ABC71E2AF",1)</f>
+        <v>=DISPIMG("ID_940CFBEED80547B5BF88692ABC71E2AF",1)</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="201.6" spans="1:4">
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/关键思路.xlsx
+++ b/关键思路.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="01.prompt" sheetId="1" r:id="rId1"/>
+    <sheet name="02.笔记" sheetId="2" r:id="rId2"/>
+    <sheet name="03_PE可视化思路" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>为我再详细解释一下你做这张图的逻辑，包括如下部分：
 1. 精准定义你对于每个色区（zone）的定义
@@ -73,6 +73,59 @@
   <si>
     <t>To assess whether th
 e proposed Pixel Embedding learns perceptually meaningful representations, we perform a controlled visualization experiment using 140 synthetic pixels partitioned into seven color zones. We first convert the RGB pixel values to the HSV color space, which separates hue (representing color type) from saturation and value. The hue channel is then quantized into seven discrete intervals to obtain perceptually motivated zone labels, following the color modeling and representation analysis approaches in Muratbekova et al. (2026) and Caron et al. (2021). Embeddings from both the baseline LLM tokenizer and our Pixel Embedding (augmented with intra-patch positional encoding and optional channel encoding) are projected into two dimensions via t-SNE or UMAP and further examined through cosine similarity matrices. This procedure enables direct visual and quantitative comparison of clustering structure between the two representation methods.</t>
+  </si>
+  <si>
+    <t>很好，我们再展开一下；
+例如有一个pixel，它由三个子通道组成(R,G,B)，那么对于一个有图像处理能力的llm（你可以选取一个，例如Qwen，Gemma），为我用清晰易懂的数学公式，给我讲解如何将一个Pixel转化为token</t>
+  </si>
+  <si>
+    <t>01 整体思路</t>
+  </si>
+  <si>
+    <t># 核心 pipeline
+Fake Data (7 Rainbow Zones) 
+    → Simulate two embedding spaces (Baseline vs Proposed)
+    → Dimensionality Reduction (t-SNE / UMAP)
+    → Visual Jitter（仅用于绘图）
+    → Side-by-side Scatter Plot + Quantitative Metrics
+    → High-DPI PNG for Paper</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>输出Tensor格式</t>
+  </si>
+  <si>
+    <t>构造140个均匀分布在7个色系的subpixel；
+每个色系平均20个</t>
+  </si>
+  <si>
+    <t>{R:[],G:[],B,[]},三个数组长度总和140</t>
+  </si>
+  <si>
+    <t>添加PE信息
+按照编码格式添加7-D Pixel Embeeding</t>
+  </si>
+  <si>
+    <t>R^{140}
+R^{140 * 1}
+R^{140 * 1 * 7}</t>
+  </si>
+  <si>
+    <t>经过LLM的embeeding层</t>
+  </si>
+  <si>
+    <t>R^{140*1*2048}[已LLAMA为例子}</t>
+  </si>
+  <si>
+    <t>t-SNE down sample</t>
+  </si>
+  <si>
+    <t>140 * 2维度点</t>
   </si>
 </sst>
 </file>
@@ -432,12 +485,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -564,7 +632,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -576,34 +644,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
@@ -688,15 +756,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1009,8 +1083,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="55.8888888888889" customWidth="1"/>
@@ -1024,7 +1098,7 @@
       </c>
     </row>
     <row r="2" ht="250" customHeight="1" spans="1:4">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -1041,6 +1115,11 @@
     <row r="3" ht="201.6" spans="1:4">
       <c r="D3" s="2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="72" spans="1:4">
+      <c r="D9" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1053,9 +1132,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="19.6851851851852" customWidth="1"/>
+    <col min="2" max="2" width="63.6018518518519" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="100.8" spans="1:2">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1065,9 +1157,157 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="21.962962962963" customWidth="1"/>
+    <col min="2" max="2" width="56.4074074074074" customWidth="1"/>
+    <col min="3" max="3" width="40.9351851851852" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="28.8" spans="1:3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="43.2" spans="1:3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/关键思路.xlsx
+++ b/关键思路.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,11 +55,127 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_489349EAC2294A34A8D4066D4271026E"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9707880" y="7929880"/>
+          <a:ext cx="7178040" cy="4152900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_272E1CA5D1244185A0C6B4ACDD1222B0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9707880" y="12821285"/>
+          <a:ext cx="7330440" cy="3070860"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_4697313344D348FB93D33BEB95D823FB"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9707880" y="15177135"/>
+          <a:ext cx="5151120" cy="2529840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_2D8A4A71A6D94E3A9EBA8D214797BC95"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9707880" y="17935575"/>
+          <a:ext cx="7368540" cy="4640580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>为我再详细解释一下你做这张图的逻辑，包括如下部分：
 1. 精准定义你对于每个色区（zone）的定义
@@ -73,6 +189,23 @@
   <si>
     <t>To assess whether th
 e proposed Pixel Embedding learns perceptually meaningful representations, we perform a controlled visualization experiment using 140 synthetic pixels partitioned into seven color zones. We first convert the RGB pixel values to the HSV color space, which separates hue (representing color type) from saturation and value. The hue channel is then quantized into seven discrete intervals to obtain perceptually motivated zone labels, following the color modeling and representation analysis approaches in Muratbekova et al. (2026) and Caron et al. (2021). Embeddings from both the baseline LLM tokenizer and our Pixel Embedding (augmented with intra-patch positional encoding and optional channel encoding) are projected into two dimensions via t-SNE or UMAP and further examined through cosine similarity matrices. This procedure enables direct visual and quantitative comparison of clustering structure between the two representation methods.</t>
+  </si>
+  <si>
+    <t>很好，现在的作图非常好；
+我们现在用数学的方式来讨论下出图的逻辑；
+先讨论左边的图，能否为我介绍一下，你是如何从140个散点，绘制出llama tokenizer后的t-SNE分布的</t>
+  </si>
+  <si>
+    <t>LLAMA 生成方式</t>
+  </si>
+  <si>
+    <t>讲解一下我的可视化思路
+构造一个16*16的patch，每个pixel由三个subpixel组成；
+也就是输入完全展开后是一个16*16*3个点组成的vector；
+然后我画出这个vector经过llama原始的tokenizer后的t-SNE分布；
+然后我画出这个vector经过我的PE后的的，t-SNE分布；
+然后我对比这两个t-SNE分布，证明PE的价值；
+基于这个假设，，你认为有什么问题吗？你认为图表上一个点代表是一个subpixel还是一个pixel？</t>
   </si>
 </sst>
 </file>
@@ -1009,8 +1142,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="55.8888888888889" customWidth="1"/>
@@ -1043,6 +1176,43 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" ht="86.4" spans="1:4">
+      <c r="C7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" ht="255.55" spans="1:4">
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="str">
+        <f>_xlfn.DISPIMG("ID_489349EAC2294A34A8D4066D4271026E",1)</f>
+        <v>=DISPIMG("ID_489349EAC2294A34A8D4066D4271026E",1)</v>
+      </c>
+    </row>
+    <row r="11" ht="115.2" spans="1:4">
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" ht="185.5" spans="1:4">
+      <c r="D13" t="str">
+        <f>_xlfn.DISPIMG("ID_272E1CA5D1244185A0C6B4ACDD1222B0",1)</f>
+        <v>=DISPIMG("ID_272E1CA5D1244185A0C6B4ACDD1222B0",1)</v>
+      </c>
+    </row>
+    <row r="14" ht="201" spans="1:4">
+      <c r="D14" t="str">
+        <f>_xlfn.DISPIMG("ID_4697313344D348FB93D33BEB95D823FB",1)</f>
+        <v>=DISPIMG("ID_4697313344D348FB93D33BEB95D823FB",1)</v>
+      </c>
+    </row>
+    <row r="15" ht="278" spans="1:4">
+      <c r="D15" t="str">
+        <f>_xlfn.DISPIMG("ID_2D8A4A71A6D94E3A9EBA8D214797BC95",1)</f>
+        <v>=DISPIMG("ID_2D8A4A71A6D94E3A9EBA8D214797BC95",1)</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
